--- a/TestData/LoginTestData.xlsx
+++ b/TestData/LoginTestData.xlsx
@@ -5,23 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasin.daiyan\AppData\Local\Programs\Maestro Studio\Maestro_Test1\Maestro-Excel-Data-Driven-Framework\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasin.daiyan\AppData\Local\Programs\Maestro Studio\Maestro_Test1\GlideGoMobileApp_InMaestro\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AC190B-488E-47FE-8E9C-7BA4DF7FDA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E336E0-D960-4586-A0B5-EEDA9A139177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
-    <sheet name="BudgetHolderLoginData" sheetId="2" r:id="rId2"/>
+    <sheet name="DriverLogin" sheetId="3" r:id="rId2"/>
+    <sheet name="Driver2Login" sheetId="4" r:id="rId3"/>
+    <sheet name="BudgetHolderLoginData" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
   <si>
     <t>email</t>
   </si>
@@ -39,6 +41,12 @@
   </si>
   <si>
     <t>sadia.hima@savethechildren.org</t>
+  </si>
+  <si>
+    <t>shah.newaj@savethechildren.org</t>
+  </si>
+  <si>
+    <t>mohai.islam@savethechildren.org</t>
   </si>
 </sst>
 </file>
@@ -99,7 +107,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -108,9 +116,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -439,7 +444,7 @@
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>12345</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -457,6 +462,86 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7336A959-F6EF-4E32-9167-6AD583D0CA5C}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.26953125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="23.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>12345</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{22FB7ACA-C65B-4438-8C94-8D4769A2B021}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D893EC52-F81E-43A8-9E01-1BBD286313DE}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.26953125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="23.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2">
+        <v>12345</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{4D954020-FBC3-41BA-AA02-1E63B8CB86AC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C58588DD-35CA-443F-B3B1-1F636C777655}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -482,7 +567,7 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>12345</v>
       </c>
       <c r="C2" s="2" t="s">
